--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto_OV.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto_OV.xlsx
@@ -8392,7 +8392,7 @@
         <v>472</v>
       </c>
       <c r="B473">
-        <v>0.4568402508427458</v>
+        <v>0.4568402508427459</v>
       </c>
       <c r="C473">
         <v>0.4817744095820801</v>
